--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.42024</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.50525</v>
-      </c>
-      <c r="I2" t="n">
-        <v>604</v>
-      </c>
-      <c r="J2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.42024</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.50525</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>40009 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.41985</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.49906</v>
-      </c>
-      <c r="I3" t="n">
-        <v>418</v>
-      </c>
-      <c r="J3" t="n">
-        <v>25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.41985</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.49906</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>40010 JULIO C.TELLO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.417631</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.492341</v>
-      </c>
-      <c r="I4" t="n">
-        <v>364</v>
-      </c>
-      <c r="J4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.417631</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.492341</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>40162 TRIBUNO FRANCISCO MOSTAJO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.411246</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.510571</v>
-      </c>
-      <c r="I5" t="n">
-        <v>228</v>
-      </c>
-      <c r="J5" t="n">
-        <v>14</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.411246</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.510571</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>40163 BENIGNO BALLON FARFAN</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.415205</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.509326</v>
-      </c>
-      <c r="I6" t="n">
-        <v>887</v>
-      </c>
-      <c r="J6" t="n">
-        <v>62</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.415205</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.509326</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>40164 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.41577</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.51263</v>
-      </c>
-      <c r="I7" t="n">
-        <v>754</v>
-      </c>
-      <c r="J7" t="n">
-        <v>57</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.41577</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.51263</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>40174 PAOLA FRASSINETTI</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.41275</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.49151999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1263</v>
-      </c>
-      <c r="J8" t="n">
-        <v>59</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.41275</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.49152</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>40178 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.4085</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.48923000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>349</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.4085</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.48923</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>40180</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-16.41719</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.51048</v>
-      </c>
-      <c r="I10" t="n">
-        <v>201</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.41719</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.51048</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>40182</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-16.41146</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.50364</v>
-      </c>
-      <c r="I11" t="n">
-        <v>254</v>
-      </c>
-      <c r="J11" t="n">
-        <v>16</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.41146</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.50364</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>40183 INDOAMERICA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-16.41304</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.49499</v>
-      </c>
-      <c r="I12" t="n">
-        <v>246</v>
-      </c>
-      <c r="J12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.41304</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.49499</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>40185 SAN JUAN BAUTISTA DE JESUS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-16.41698</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.50275000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>239</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-16.41698</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.50275</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>40211 HEROES DEL PACIFICO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-16.41956</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.48415</v>
-      </c>
-      <c r="I14" t="n">
-        <v>548</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-16.41956</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.48415</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>40220 HEROES DEL CENEPA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-16.42672</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.49751000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>263</v>
-      </c>
-      <c r="J15" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-16.42672</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.49751</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>40300 MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-16.410826</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.48330900000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>426</v>
-      </c>
-      <c r="J16" t="n">
-        <v>30</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-16.410826</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.483309</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>40315 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-16.41568</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.48571</v>
-      </c>
-      <c r="I17" t="n">
-        <v>372</v>
-      </c>
-      <c r="J17" t="n">
-        <v>25</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-16.41568</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.48571</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>COAR AREQUIPA / JOSE TEOBALDO PAREDES VALDEZ</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-16.412236</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.49881000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>463</v>
-      </c>
-      <c r="J18" t="n">
-        <v>47</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-16.412236</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.49881</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>MIGUEL GRAU A</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-16.40948</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.48575</v>
-      </c>
-      <c r="I19" t="n">
-        <v>202</v>
-      </c>
-      <c r="J19" t="n">
-        <v>14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-16.40948</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.48575</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>NEPTALI VALDERRAMA AMPUERO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-16.42276</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.51604</v>
-      </c>
-      <c r="I20" t="n">
-        <v>925</v>
-      </c>
-      <c r="J20" t="n">
-        <v>55</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-16.42276</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.51604</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>PROGRESISTA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-16.4112</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.50406</v>
-      </c>
-      <c r="I21" t="n">
-        <v>115</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-16.4112</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.50406</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>JUAN XXIII</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-16.40728</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.48703</v>
-      </c>
-      <c r="I22" t="n">
-        <v>471</v>
-      </c>
-      <c r="J22" t="n">
-        <v>37</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-16.40728</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.48703</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>NUESTRA SEÑORA DE COPACABANA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-16.421341</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.495912</v>
-      </c>
-      <c r="I23" t="n">
-        <v>246</v>
-      </c>
-      <c r="J23" t="n">
-        <v>16</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-16.421341</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.495912</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-16.40677</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-71.48053</v>
-      </c>
-      <c r="I24" t="n">
-        <v>555</v>
-      </c>
-      <c r="J24" t="n">
-        <v>39</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-16.40677</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-71.48053</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>PADRE PEREZ DE GUEREÑU</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-16.42019</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-71.49356899999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>894</v>
-      </c>
-      <c r="J25" t="n">
-        <v>49</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-16.42019</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-71.493569</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>PAULO VI</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-16.42198</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-71.48815999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>276</v>
-      </c>
-      <c r="J26" t="n">
-        <v>17</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-16.42198</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-71.48816</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-16.410543</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-71.49663200000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>583</v>
-      </c>
-      <c r="J27" t="n">
-        <v>38</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-16.410543</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-71.496632</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SANTA MARIA DE LA PAZ</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-16.43384</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-71.49112</v>
-      </c>
-      <c r="I28" t="n">
-        <v>714</v>
-      </c>
-      <c r="J28" t="n">
-        <v>40</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-16.43384</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-71.49112</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>SOR ANA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-16.41403</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-71.48291</v>
-      </c>
-      <c r="I29" t="n">
-        <v>927</v>
-      </c>
-      <c r="J29" t="n">
-        <v>44</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-16.41403</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-71.48291</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>VIRGEN DE CHAPI</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-16.425582</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-71.49621999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>329</v>
-      </c>
-      <c r="J30" t="n">
-        <v>21</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-16.425582</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-71.49622</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>LATINOAMERICANO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-16.41942</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-71.49826</v>
-      </c>
-      <c r="I31" t="n">
-        <v>956</v>
-      </c>
-      <c r="J31" t="n">
-        <v>59</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-16.41942</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-71.49826</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SAN SEBASTIAN</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-16.418986</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-71.499906</v>
-      </c>
-      <c r="I32" t="n">
-        <v>219</v>
-      </c>
-      <c r="J32" t="n">
-        <v>20</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-16.418986</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-71.499906</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>40696 / 40696 SANTA MARIA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-16.43496</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-71.48605999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>200</v>
-      </c>
-      <c r="J33" t="n">
-        <v>13</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-16.43496</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-71.48606</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>NUESTRA SEÑORA DE LA SOLIDARIDAD</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-16.41415</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-71.48908</v>
-      </c>
-      <c r="I34" t="n">
-        <v>222</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-16.41415</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-71.48908</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>ADONAI INTERNACIONAL</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-16.425953</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-71.50982</v>
-      </c>
-      <c r="I35" t="n">
-        <v>200</v>
-      </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-16.425953</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-71.50982</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>GRAN PADRE AMADO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-16.417293</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-71.479231</v>
-      </c>
-      <c r="I36" t="n">
-        <v>210</v>
-      </c>
-      <c r="J36" t="n">
-        <v>14</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-16.417293</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-71.479231</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>MARIA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-16.41789</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-71.49288</v>
-      </c>
-      <c r="I37" t="n">
-        <v>41</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-16.41789</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-71.49288</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>MARIA DEL REDENTOR</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-16.41796</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-71.50346999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>207</v>
-      </c>
-      <c r="J38" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-16.41796</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-71.50347</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>ROBERT F. KENNEDY</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-16.41834</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-71.5087</v>
-      </c>
-      <c r="I39" t="n">
-        <v>664</v>
-      </c>
-      <c r="J39" t="n">
-        <v>28</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-16.41834</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-71.5087</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>JOULE DIVINO NIÑO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-16.4179</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-71.4966</v>
-      </c>
-      <c r="I40" t="n">
-        <v>393</v>
-      </c>
-      <c r="J40" t="n">
-        <v>33</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-16.4179</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-71.4966</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>DEL SOLAR</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-16.41839</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-71.50919</v>
-      </c>
-      <c r="I41" t="n">
-        <v>227</v>
-      </c>
-      <c r="J41" t="n">
-        <v>18</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-16.41839</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-71.50919</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55506</t>
+          <t>62597</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>40183 INDOAMERICA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.42024</t>
+          <t>-16.41304</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.50525</t>
+          <t>-71.49499</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62451</t>
+          <t>550035</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40009 SAN MARTIN DE PORRES</t>
+          <t>40696 / 40696 SANTA MARIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.41985</t>
+          <t>-16.43496</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.49906</t>
+          <t>-71.48606</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>62494</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40010 JULIO C.TELLO</t>
+          <t>40162 TRIBUNO FRANCISCO MOSTAJO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.417631</t>
+          <t>-16.411246</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.492341</t>
+          <t>-71.510571</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40162 TRIBUNO FRANCISCO MOSTAJO</t>
+          <t>MIGUEL GRAU A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.411246</t>
+          <t>-16.40948</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.510571</t>
+          <t>-71.48575</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62502</t>
+          <t>551006</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40163 BENIGNO BALLON FARFAN</t>
+          <t>GRAN PADRE AMADO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.415205</t>
+          <t>-16.417293</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.509326</t>
+          <t>-71.479231</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>62583</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40164 JOSE CARLOS MARIATEGUI</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.41577</t>
+          <t>-16.41146</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.51263</t>
+          <t>-71.50364</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62521</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40174 PAOLA FRASSINETTI</t>
+          <t>NUESTRA SEÑORA DE COPACABANA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.41275</t>
+          <t>-16.421341</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.49152</t>
+          <t>-71.495912</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>62540</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40178 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.4085</t>
+          <t>-16.41719</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.48923</t>
+          <t>-71.51048</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62564</t>
+          <t>62936</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>PAULO VI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.41719</t>
+          <t>-16.42198</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.51048</t>
+          <t>-71.48816</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62583</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40182</t>
+          <t>40185 SAN JUAN BAUTISTA DE JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.41146</t>
+          <t>-16.41698</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.50364</t>
+          <t>-71.50275</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>62597</t>
+          <t>856861</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>40183 INDOAMERICA</t>
+          <t>DEL SOLAR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.41304</t>
+          <t>-16.41839</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.49499</t>
+          <t>-71.50919</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40185 SAN JUAN BAUTISTA DE JESUS</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.41698</t>
+          <t>-16.418986</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.50275</t>
+          <t>-71.499906</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62620</t>
+          <t>550714</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40211 HEROES DEL PACIFICO</t>
+          <t>ADONAI INTERNACIONAL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.41956</t>
+          <t>-16.425953</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.48415</t>
+          <t>-71.50982</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62639</t>
+          <t>62540</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40220 HEROES DEL CENEPA</t>
+          <t>40178 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.42672</t>
+          <t>-16.4085</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.49751</t>
+          <t>-71.48923</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>63002</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40300 MIGUEL GRAU</t>
+          <t>VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.410826</t>
+          <t>-16.425582</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.483309</t>
+          <t>-71.49622</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>62451</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40315 JOSE MARIA ARGUEDAS</t>
+          <t>40009 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.41568</t>
+          <t>-16.41985</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.48571</t>
+          <t>-71.49906</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>62762</t>
+          <t>62658</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COAR AREQUIPA / JOSE TEOBALDO PAREDES VALDEZ</t>
+          <t>40315 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.412236</t>
+          <t>-16.41568</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.49881</t>
+          <t>-71.48571</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62804</t>
+          <t>803009</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU A</t>
+          <t>ROBERT F. KENNEDY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.40948</t>
+          <t>-16.41834</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.48575</t>
+          <t>-71.5087</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>664</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62823</t>
+          <t>62644</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NEPTALI VALDERRAMA AMPUERO</t>
+          <t>40300 MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.42276</t>
+          <t>-16.410826</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.51604</t>
+          <t>-71.483309</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>426</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62837</t>
+          <t>62465</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PROGRESISTA</t>
+          <t>40010 JULIO C.TELLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.4112</t>
+          <t>-16.417631</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.50406</t>
+          <t>-71.492341</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>62861</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>40220 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.40728</t>
+          <t>-16.42672</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.48703</t>
+          <t>-71.49751</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>62880</t>
+          <t>803325</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE COPACABANA</t>
+          <t>JOULE DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.421341</t>
+          <t>-16.4179</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.495912</t>
+          <t>-71.4966</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62903</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOURDES</t>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.40677</t>
+          <t>-16.42024</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.48053</t>
+          <t>-71.50525</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>604</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>62861</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PADRE PEREZ DE GUEREÑU</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.42019</t>
+          <t>-16.40728</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.493569</t>
+          <t>-71.48703</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>471</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>62941</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PAULO VI</t>
+          <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.42198</t>
+          <t>-16.410543</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.48816</t>
+          <t>-71.496632</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>583</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62941</t>
+          <t>62903</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN PEDRO Y SAN PABLO</t>
+          <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.410543</t>
+          <t>-16.40677</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.496632</t>
+          <t>-71.48053</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>555</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>62960</t>
+          <t>615287</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE LA PAZ</t>
+          <t>MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.43384</t>
+          <t>-16.41789</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.49112</t>
+          <t>-71.49288</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>706598</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SOR ANA</t>
+          <t>MARIA DEL REDENTOR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.41403</t>
+          <t>-16.41796</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.48291</t>
+          <t>-71.50347</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>63002</t>
+          <t>62960</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>VIRGEN DE CHAPI</t>
+          <t>SANTA MARIA DE LA PAZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.425582</t>
+          <t>-16.43384</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.49622</t>
+          <t>-71.49112</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>714</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>63101</t>
+          <t>62620</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LATINOAMERICANO</t>
+          <t>40211 HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.41942</t>
+          <t>-16.41956</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.49826</t>
+          <t>-71.48415</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>63163</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN</t>
+          <t>SOR ANA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.418986</t>
+          <t>-16.41403</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.499906</t>
+          <t>-71.48291</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>927</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>550035</t>
+          <t>62762</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>40696 / 40696 SANTA MARIA</t>
+          <t>COAR AREQUIPA / JOSE TEOBALDO PAREDES VALDEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.43496</t>
+          <t>-16.412236</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.48606</t>
+          <t>-71.49881</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>550337</t>
+          <t>62922</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA SOLIDARIDAD</t>
+          <t>PADRE PEREZ DE GUEREÑU</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-16.41415</t>
+          <t>-16.42019</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.48908</t>
+          <t>-71.493569</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>894</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>550714</t>
+          <t>62823</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADONAI INTERNACIONAL</t>
+          <t>NEPTALI VALDERRAMA AMPUERO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.425953</t>
+          <t>-16.42276</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.50982</t>
+          <t>-71.51604</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>925</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>551006</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GRAN PADRE AMADO</t>
+          <t>40164 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-16.417293</t>
+          <t>-16.41577</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-71.479231</t>
+          <t>-71.51263</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>754</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>615287</t>
+          <t>62521</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MARIA DEL ROSARIO</t>
+          <t>40174 PAOLA FRASSINETTI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.41789</t>
+          <t>-16.41275</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-71.49288</t>
+          <t>-71.49152</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>706598</t>
+          <t>63101</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MARIA DEL REDENTOR</t>
+          <t>LATINOAMERICANO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.41796</t>
+          <t>-16.41942</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.50347</t>
+          <t>-71.49826</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>956</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>803009</t>
+          <t>62837</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ROBERT F. KENNEDY</t>
+          <t>PROGRESISTA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.41834</t>
+          <t>-16.4112</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.5087</t>
+          <t>-71.50406</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>803325</t>
+          <t>62502</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JOULE DIVINO NIÑO</t>
+          <t>40163 BENIGNO BALLON FARFAN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.4179</t>
+          <t>-16.415205</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.4966</t>
+          <t>-71.509326</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>887</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>856861</t>
+          <t>550337</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DEL SOLAR</t>
+          <t>NUESTRA SEÑORA DE LA SOLIDARIDAD</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-16.41839</t>
+          <t>-16.41415</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.50919</t>
+          <t>-71.48908</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>62597</t>
+          <t>856861</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40183 INDOAMERICA</t>
+          <t>DEL SOLAR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.41304</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.49499</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-16.41839</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-71.50919</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>550035</t>
+          <t>803325</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40696 / 40696 SANTA MARIA</t>
+          <t>JOULE DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.43496</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.48606</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-16.4179</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-71.4966</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>803009</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40162 TRIBUNO FRANCISCO MOSTAJO</t>
+          <t>ROBERT F. KENNEDY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.411246</t>
+          <t>664</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.510571</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-16.41834</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.5087</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>62804</t>
+          <t>706598</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU A</t>
+          <t>MARIA DEL REDENTOR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.40948</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.48575</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-16.41796</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.50347</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>551006</t>
+          <t>615287</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GRAN PADRE AMADO</t>
+          <t>MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.417293</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.479231</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-16.41789</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.49288</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62583</t>
+          <t>551006</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40182</t>
+          <t>GRAN PADRE AMADO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.41146</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.50364</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-16.417293</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.479231</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62880</t>
+          <t>550714</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE COPACABANA</t>
+          <t>ADONAI INTERNACIONAL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.421341</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.495912</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-16.425953</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.50982</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>62564</t>
+          <t>550337</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>NUESTRA SEÑORA DE LA SOLIDARIDAD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.41719</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.51048</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-16.41415</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.48908</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>550035</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PAULO VI</t>
+          <t>40696 / 40696 SANTA MARIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-16.42198</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.48816</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>-16.43496</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.48606</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>063163</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40185 SAN JUAN BAUTISTA DE JESUS</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.41698</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.50275</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-16.418986</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.499906</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>856861</t>
+          <t>063101</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DEL SOLAR</t>
+          <t>LATINOAMERICANO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.41839</t>
+          <t>956</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.50919</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-16.41942</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.49826</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>63163</t>
+          <t>063002</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN</t>
+          <t>VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-16.418986</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.499906</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-16.425582</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.49622</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>550714</t>
+          <t>062984</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADONAI INTERNACIONAL</t>
+          <t>SOR ANA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-16.425953</t>
+          <t>927</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.50982</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-16.41403</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-71.48291</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62540</t>
+          <t>062960</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40178 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>SANTA MARIA DE LA PAZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-16.4085</t>
+          <t>714</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.48923</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-16.43384</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.49112</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63002</t>
+          <t>062941</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VIRGEN DE CHAPI</t>
+          <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-16.425582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.49622</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-16.410543</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.496632</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62451</t>
+          <t>062936</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40009 SAN MARTIN DE PORRES</t>
+          <t>PAULO VI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-16.41985</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.49906</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-16.42198</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.48816</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>62658</t>
+          <t>062922</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40315 JOSE MARIA ARGUEDAS</t>
+          <t>PADRE PEREZ DE GUEREÑU</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-16.41568</t>
+          <t>894</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.48571</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-16.42019</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.493569</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>803009</t>
+          <t>062903</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ROBERT F. KENNEDY</t>
+          <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-16.41834</t>
+          <t>555</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.5087</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>-16.40677</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-71.48053</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>062880</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40300 MIGUEL GRAU</t>
+          <t>NUESTRA SEÑORA DE COPACABANA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-16.410826</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.483309</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>-16.421341</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.495912</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>062861</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40010 JULIO C.TELLO</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-16.417631</t>
+          <t>471</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.492341</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>-16.40728</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.48703</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>62639</t>
+          <t>062837</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40220 HEROES DEL CENEPA</t>
+          <t>PROGRESISTA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-16.42672</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.49751</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-16.4112</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.50406</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>803325</t>
+          <t>062823</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JOULE DIVINO NIÑO</t>
+          <t>NEPTALI VALDERRAMA AMPUERO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-16.4179</t>
+          <t>925</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.4966</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-16.42276</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-71.51604</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>55506</t>
+          <t>062804</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>MIGUEL GRAU A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-16.42024</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.50525</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>-16.40948</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-71.48575</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>62861</t>
+          <t>062762</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>COAR AREQUIPA / JOSE TEOBALDO PAREDES VALDEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-16.40728</t>
+          <t>463</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.48703</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>-16.412236</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-71.49881</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>62941</t>
+          <t>062658</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAN PEDRO Y SAN PABLO</t>
+          <t>40315 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-16.410543</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.496632</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>-16.41568</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-71.48571</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62903</t>
+          <t>062644</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOURDES</t>
+          <t>40300 MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-16.40677</t>
+          <t>426</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.48053</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>-16.410826</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-71.483309</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>615287</t>
+          <t>062639</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MARIA DEL ROSARIO</t>
+          <t>40220 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-16.41789</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.49288</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-16.42672</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-71.49751</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>706598</t>
+          <t>062620</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MARIA DEL REDENTOR</t>
+          <t>40211 HEROES DEL PACIFICO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-16.41796</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.50347</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-16.41956</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-71.48415</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>62960</t>
+          <t>062615</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE LA PAZ</t>
+          <t>40185 SAN JUAN BAUTISTA DE JESUS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-16.43384</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.49112</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>-16.41698</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-71.50275</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>62620</t>
+          <t>062597</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40211 HEROES DEL PACIFICO</t>
+          <t>40183 INDOAMERICA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-16.41956</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.48415</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-16.41304</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-71.49499</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>062583</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SOR ANA</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-16.41403</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.48291</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>-16.41146</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-71.50364</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>62762</t>
+          <t>062564</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>COAR AREQUIPA / JOSE TEOBALDO PAREDES VALDEZ</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-16.412236</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.49881</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>-16.41719</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-71.51048</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>062540</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PADRE PEREZ DE GUEREÑU</t>
+          <t>40178 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-16.42019</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.493569</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>-16.4085</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-71.48923</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62823</t>
+          <t>062521</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NEPTALI VALDERRAMA AMPUERO</t>
+          <t>40174 PAOLA FRASSINETTI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-16.42276</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.51604</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>-16.41275</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-71.49152</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>062516</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2619,22 +2619,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>-16.41577</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-71.51263</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>62521</t>
+          <t>062502</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>40174 PAOLA FRASSINETTI</t>
+          <t>40163 BENIGNO BALLON FARFAN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-16.41275</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-71.49152</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>-16.415205</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-71.509326</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>63101</t>
+          <t>062494</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LATINOAMERICANO</t>
+          <t>40162 TRIBUNO FRANCISCO MOSTAJO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-16.41942</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.49826</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>-16.411246</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-71.510571</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>62837</t>
+          <t>062465</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PROGRESISTA</t>
+          <t>40010 JULIO C.TELLO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-16.4112</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.50406</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>-16.417631</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-71.492341</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>62502</t>
+          <t>062451</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>40163 BENIGNO BALLON FARFAN</t>
+          <t>40009 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-16.415205</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.509326</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>-16.41985</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-71.49906</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>550337</t>
+          <t>055506</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA SOLIDARIDAD</t>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-16.41415</t>
+          <t>604</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.48908</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-16.42024</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-71.50525</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">

--- a/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
+++ b/ZonasEscolares/excels/AREQUIPA-AREQUIPA-PAUCARPATA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
